--- a/public/system/export/device.xlsx
+++ b/public/system/export/device.xlsx
@@ -1,20 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12210"/>
+    <workbookView xWindow="240" yWindow="570" windowWidth="24615" windowHeight="11955"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet0" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="124519"/>
+  <extLst>
+    <ext uri="GoogleSheetsCustomDataVersion2">
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="lDT5JqXZt4NKODR45x6Wo13oR1bg0vRusL1x2CP3qp8="/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>STT</t>
   </si>
@@ -22,15 +27,6 @@
     <t>Tên Thiết Bị</t>
   </si>
   <si>
-    <t>Nước sản xuất</t>
-  </si>
-  <si>
-    <t>Năm sản xuất</t>
-  </si>
-  <si>
-    <t>Số  lượng</t>
-  </si>
-  <si>
     <t>Đơn Vị</t>
   </si>
   <si>
@@ -46,82 +42,54 @@
     <t>Bộ môn</t>
   </si>
   <si>
-    <t>Phân loại</t>
-  </si>
-  <si>
-    <t>Ống nghiệm Φ12</t>
+    <t>SỞ GD&amp;ĐT ...</t>
+  </si>
+  <si>
+    <t>CỘNG HÒA XÃ HỘI CHỦ NGHĨA VIỆT NAM</t>
+  </si>
+  <si>
+    <t>TRƯỜNG …</t>
+  </si>
+  <si>
+    <t>Độc lập - Tự do - Hạnh phúc</t>
+  </si>
+  <si>
+    <t>Bàn thực hành</t>
   </si>
   <si>
     <t>Cái</t>
   </si>
   <si>
-    <t>Phòng Tiếng Anh</t>
-  </si>
-  <si>
-    <t>Vật Lý-Trải nghiệm</t>
-  </si>
-  <si>
-    <t>Thiết bị</t>
-  </si>
-  <si>
-    <t>Ống nghiệm Φ16</t>
-  </si>
-  <si>
-    <t>Hỏng 15</t>
-  </si>
-  <si>
-    <t>Ống nghiệm Φ20</t>
-  </si>
-  <si>
-    <t>cái</t>
-  </si>
-  <si>
-    <t>Hỏng 35</t>
-  </si>
-  <si>
-    <t>Ống nghiệm Φ16 có nhánh</t>
-  </si>
-  <si>
-    <t>Ống nghiệm Φ24 có nhánh</t>
-  </si>
-  <si>
-    <t>Ống nghiệm 2 nhánh chữ Y</t>
-  </si>
-  <si>
-    <t>Ống hút nhỏ giọt</t>
-  </si>
-  <si>
-    <t>Hỏng 06</t>
-  </si>
-  <si>
-    <t>Ống đong hình trụ 100ml</t>
-  </si>
-  <si>
-    <t>Hỏng 08</t>
-  </si>
-  <si>
-    <t>Ống hình trụ rỗng 2 đầu</t>
-  </si>
-  <si>
-    <t>Ống thuỷ tinh hình trụ loe 1 đầu</t>
+    <t>Thiết bị môn Công nghệ - NN</t>
+  </si>
+  <si>
+    <t>Công nghệ -CN và NN</t>
+  </si>
+  <si>
+    <t>Hỏng 02</t>
+  </si>
+  <si>
+    <t>Ngày xuất:</t>
+  </si>
+  <si>
+    <t>DANH SÁCH THIẾT BỊ</t>
+  </si>
+  <si>
+    <t>Năm SX</t>
+  </si>
+  <si>
+    <t>Số lượng</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
-  <numFmts count="4">
-    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="23">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="9">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -129,361 +97,64 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
+      <b/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Arial"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="15"/>
-      <color theme="3"/>
+      <color theme="1"/>
       <name val="Arial"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="3"/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <charset val="0"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -493,526 +164,97 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color indexed="64"/>
       </left>
       <right style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color indexed="64"/>
       </right>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color indexed="64"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF000000"/>
       </right>
       <top style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+  </cellStyleXfs>
+  <cellXfs count="20">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-  </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Currency" xfId="2" builtinId="4"/>
-    <cellStyle name="Percent" xfId="3" builtinId="5"/>
-    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
-    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
-    <cellStyle name="Note" xfId="8" builtinId="10"/>
-    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
-    <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Input" xfId="16" builtinId="20"/>
-    <cellStyle name="Output" xfId="17" builtinId="21"/>
-    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
-    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
-    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
-    <cellStyle name="Total" xfId="21" builtinId="25"/>
-    <cellStyle name="Good" xfId="22" builtinId="26"/>
-    <cellStyle name="Bad" xfId="23" builtinId="27"/>
-    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
-    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
-    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
-    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="17">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="double">
-          <color theme="4"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4"/>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <left style="thin">
-          <color theme="4"/>
-        </left>
-        <right style="thin">
-          <color theme="4"/>
-        </right>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-        <horizontal style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-  </dxfs>
-  <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
-    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="6"/>
-      <tableStyleElement type="headerRow" dxfId="5"/>
-      <tableStyleElement type="totalRow" dxfId="4"/>
-      <tableStyleElement type="firstColumn" dxfId="3"/>
-      <tableStyleElement type="lastColumn" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
-    </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="16"/>
-      <tableStyleElement type="totalRow" dxfId="15"/>
-      <tableStyleElement type="firstRowStripe" dxfId="14"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
-      <tableStyleElement type="pageFieldValues" dxfId="7"/>
-    </tableStyle>
-  </tableStyles>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
 </styleSheet>
 </file>
 
@@ -1208,382 +450,291 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:K1000"/>
-  <sheetFormatPr defaultColWidth="12.6285714285714" defaultRowHeight="15" customHeight="1"/>
+  <dimension ref="A1:I1008"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="12.6285714285714" customWidth="1"/>
-    <col min="2" max="2" width="34.247619047619" customWidth="1"/>
-    <col min="3" max="3" width="15.2857142857143" customWidth="1"/>
-    <col min="4" max="6" width="12.6285714285714" customWidth="1"/>
-    <col min="10" max="10" width="18.247619047619" customWidth="1"/>
+    <col min="1" max="1" width="5.7109375" customWidth="1"/>
+    <col min="2" max="2" width="30.5703125" customWidth="1"/>
+    <col min="3" max="3" width="10.85546875" customWidth="1"/>
+    <col min="4" max="4" width="10.140625" customWidth="1"/>
+    <col min="5" max="5" width="8.140625" customWidth="1"/>
+    <col min="6" max="6" width="8.5703125" customWidth="1"/>
+    <col min="7" max="7" width="12.28515625" customWidth="1"/>
+    <col min="8" max="8" width="25.42578125" customWidth="1"/>
+    <col min="9" max="9" width="21.5703125" customWidth="1"/>
+    <col min="13" max="13" width="12.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1" spans="1:11">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:9" ht="15" customHeight="1">
+      <c r="A1" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="16"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+    </row>
+    <row r="2" spans="1:9" ht="15" customHeight="1">
+      <c r="A2" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="16"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
+      <c r="I2" s="18"/>
+    </row>
+    <row r="3" spans="1:9" ht="15" customHeight="1">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+    </row>
+    <row r="4" spans="1:9" ht="25.5" customHeight="1">
+      <c r="A4" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="17"/>
+      <c r="H4" s="17"/>
+      <c r="I4" s="17"/>
+    </row>
+    <row r="5" spans="1:9" ht="15" customHeight="1">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+    </row>
+    <row r="6" spans="1:9" ht="15" customHeight="1">
+      <c r="A6" s="1"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="9"/>
+      <c r="H6" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="I6" s="19"/>
+    </row>
+    <row r="9" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A9" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B9" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C9" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F9" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G9" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H9" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I9" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+    </row>
+    <row r="10" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A10" s="12">
+        <v>1</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="14">
+        <v>2021</v>
+      </c>
+      <c r="D10" s="14">
+        <v>10</v>
+      </c>
+      <c r="E10" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" s="14">
+        <v>250</v>
+      </c>
+      <c r="G10" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H10" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I10" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A11" s="11">
+        <v>2</v>
+      </c>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+    </row>
+    <row r="12" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A12" s="11">
+        <v>3</v>
+      </c>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+    </row>
+    <row r="13" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A13" s="11">
+        <v>4</v>
+      </c>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+    </row>
+    <row r="14" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A14" s="11">
+        <v>5</v>
+      </c>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
+    </row>
+    <row r="15" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A15" s="11">
+        <v>6</v>
+      </c>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+    </row>
+    <row r="16" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A16" s="11">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
+    </row>
+    <row r="17" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A17" s="11">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+    </row>
+    <row r="18" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A18" s="11">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="4"/>
+    </row>
+    <row r="19" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A19" s="11">
         <v>10</v>
       </c>
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="4"/>
     </row>
-    <row r="2" ht="15.75" customHeight="1" spans="1:11">
-      <c r="A2" s="2">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" s="2">
-        <v>2007</v>
-      </c>
-      <c r="E2" s="2">
-        <v>50</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" s="2">
-        <v>3</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" ht="15.75" customHeight="1" spans="1:11">
-      <c r="A3" s="2">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="2">
-        <v>2007</v>
-      </c>
-      <c r="E3" s="2">
-        <v>35</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3" s="2">
-        <v>5</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" ht="15.75" customHeight="1" spans="1:11">
-      <c r="A4" s="2">
-        <v>3</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" s="2">
-        <v>2007</v>
-      </c>
-      <c r="E4" s="2">
-        <v>65</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G4" s="2">
-        <v>5</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" ht="15.75" customHeight="1" spans="1:11">
-      <c r="A5" s="2">
-        <v>4</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5" s="2">
-        <v>2007</v>
-      </c>
-      <c r="E5" s="2">
-        <v>12</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5" s="2">
-        <v>1.61</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" ht="15.75" customHeight="1" spans="1:11">
-      <c r="A6" s="2">
-        <v>5</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" s="2">
-        <v>2007</v>
-      </c>
-      <c r="E6" s="2">
-        <v>8</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6" s="2">
-        <v>3</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" ht="15.75" customHeight="1" spans="1:11">
-      <c r="A7" s="2">
-        <v>6</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7" s="2">
-        <v>2007</v>
-      </c>
-      <c r="E7" s="2">
-        <v>11</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7" s="2">
-        <v>3</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" ht="15.75" customHeight="1" spans="1:11">
-      <c r="A8" s="2">
-        <v>7</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D8" s="2">
-        <v>2007</v>
-      </c>
-      <c r="E8" s="2">
-        <v>6</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G8" s="2">
-        <v>6.5</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" ht="15.75" customHeight="1" spans="1:11">
-      <c r="A9" s="2">
-        <v>8</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D9" s="2">
-        <v>2007</v>
-      </c>
-      <c r="E9" s="2">
-        <v>18</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G9" s="2">
-        <v>8</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" ht="15.75" customHeight="1" spans="1:11">
-      <c r="A10" s="2">
-        <v>9</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D10" s="2">
-        <v>2007</v>
-      </c>
-      <c r="E10" s="2">
-        <v>12</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G10" s="2">
-        <v>2.54</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="11" ht="15.75" customHeight="1" spans="1:11">
-      <c r="A11" s="2">
-        <v>10</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D11" s="2">
-        <v>2007</v>
-      </c>
-      <c r="E11" s="2">
-        <v>26</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G11" s="2">
-        <v>8</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="12" ht="15.75" customHeight="1"/>
-    <row r="13" ht="15.75" customHeight="1"/>
-    <row r="14" ht="15.75" customHeight="1"/>
-    <row r="15" ht="15.75" customHeight="1"/>
-    <row r="16" ht="15.75" customHeight="1"/>
-    <row r="17" ht="15.75" customHeight="1"/>
-    <row r="18" ht="15.75" customHeight="1"/>
-    <row r="19" ht="15.75" customHeight="1"/>
-    <row r="20" ht="15.75" customHeight="1"/>
-    <row r="21" ht="15.75" customHeight="1"/>
-    <row r="22" ht="15.75" customHeight="1"/>
-    <row r="23" ht="15.75" customHeight="1"/>
-    <row r="24" ht="15.75" customHeight="1"/>
-    <row r="25" ht="15.75" customHeight="1"/>
-    <row r="26" ht="15.75" customHeight="1"/>
-    <row r="27" ht="15.75" customHeight="1"/>
-    <row r="28" ht="15.75" customHeight="1"/>
-    <row r="29" ht="15.75" customHeight="1"/>
-    <row r="30" ht="15.75" customHeight="1"/>
-    <row r="31" ht="15.75" customHeight="1"/>
-    <row r="32" ht="15.75" customHeight="1"/>
+    <row r="20" spans="1:9" ht="15.75" customHeight="1"/>
+    <row r="21" spans="1:9" ht="15.75" customHeight="1"/>
+    <row r="22" spans="1:9" ht="15.75" customHeight="1"/>
+    <row r="23" spans="1:9" ht="15.75" customHeight="1"/>
+    <row r="24" spans="1:9" ht="15.75" customHeight="1"/>
+    <row r="25" spans="1:9" ht="15.75" customHeight="1"/>
+    <row r="26" spans="1:9" ht="15.75" customHeight="1"/>
+    <row r="27" spans="1:9" ht="15.75" customHeight="1"/>
+    <row r="28" spans="1:9" ht="15.75" customHeight="1"/>
+    <row r="29" spans="1:9" ht="15.75" customHeight="1"/>
+    <row r="30" spans="1:9" ht="15.75" customHeight="1"/>
+    <row r="31" spans="1:9" ht="15.75" customHeight="1"/>
+    <row r="32" spans="1:9" ht="15.75" customHeight="1"/>
     <row r="33" ht="15.75" customHeight="1"/>
     <row r="34" ht="15.75" customHeight="1"/>
     <row r="35" ht="15.75" customHeight="1"/>
@@ -2552,8 +1703,23 @@
     <row r="998" ht="15.75" customHeight="1"/>
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
+    <row r="1001" ht="15.75" customHeight="1"/>
+    <row r="1002" ht="15.75" customHeight="1"/>
+    <row r="1003" ht="15.75" customHeight="1"/>
+    <row r="1004" ht="15.75" customHeight="1"/>
+    <row r="1005" ht="15.75" customHeight="1"/>
+    <row r="1006" ht="15.75" customHeight="1"/>
+    <row r="1007" ht="15.75" customHeight="1"/>
+    <row r="1008" ht="15.75" customHeight="1"/>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
+  <mergeCells count="5">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A4:I4"/>
+    <mergeCell ref="E1:I1"/>
+    <mergeCell ref="E2:I2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
--- a/public/system/export/device.xlsx
+++ b/public/system/export/device.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>STT</t>
   </si>
@@ -52,21 +52,6 @@
   </si>
   <si>
     <t>Độc lập - Tự do - Hạnh phúc</t>
-  </si>
-  <si>
-    <t>Bàn thực hành</t>
-  </si>
-  <si>
-    <t>Cái</t>
-  </si>
-  <si>
-    <t>Thiết bị môn Công nghệ - NN</t>
-  </si>
-  <si>
-    <t>Công nghệ -CN và NN</t>
-  </si>
-  <si>
-    <t>Hỏng 02</t>
   </si>
   <si>
     <t>Ngày xuất:</t>
@@ -237,6 +222,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -245,9 +233,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -475,34 +460,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15" customHeight="1">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="16"/>
+      <c r="B1" s="17"/>
       <c r="C1" s="3"/>
       <c r="D1" s="3"/>
-      <c r="E1" s="18" t="s">
+      <c r="E1" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="16"/>
+      <c r="B2" s="17"/>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
-      <c r="E2" s="18" t="s">
+      <c r="E2" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
-      <c r="I2" s="18"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
+      <c r="I2" s="19"/>
     </row>
     <row r="3" spans="1:9" ht="15" customHeight="1">
       <c r="A3" s="1"/>
@@ -514,17 +499,17 @@
       <c r="G3" s="1"/>
     </row>
     <row r="4" spans="1:9" ht="25.5" customHeight="1">
-      <c r="A4" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="17"/>
-      <c r="H4" s="17"/>
-      <c r="I4" s="17"/>
+      <c r="A4" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
+      <c r="G4" s="18"/>
+      <c r="H4" s="18"/>
+      <c r="I4" s="18"/>
     </row>
     <row r="5" spans="1:9" ht="15" customHeight="1">
       <c r="A5" s="1"/>
@@ -543,9 +528,9 @@
       <c r="F6" s="8"/>
       <c r="G6" s="9"/>
       <c r="H6" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="I6" s="19"/>
+        <v>11</v>
+      </c>
+      <c r="I6" s="16"/>
     </row>
     <row r="9" spans="1:9" ht="15.75" customHeight="1">
       <c r="A9" s="6" t="s">
@@ -555,10 +540,10 @@
         <v>1</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E9" s="6" t="s">
         <v>2</v>
@@ -580,30 +565,14 @@
       <c r="A10" s="12">
         <v>1</v>
       </c>
-      <c r="B10" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" s="14">
-        <v>2021</v>
-      </c>
-      <c r="D10" s="14">
-        <v>10</v>
-      </c>
-      <c r="E10" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="F10" s="14">
-        <v>250</v>
-      </c>
-      <c r="G10" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="H10" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I10" s="13" t="s">
-        <v>14</v>
-      </c>
+      <c r="B10" s="13"/>
+      <c r="C10" s="14"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="14"/>
+      <c r="F10" s="14"/>
+      <c r="G10" s="15"/>
+      <c r="H10" s="13"/>
+      <c r="I10" s="13"/>
     </row>
     <row r="11" spans="1:9" ht="15.75" customHeight="1">
       <c r="A11" s="11">
